--- a/mode_docx_gen/pmi_gz/dtm_modes/ДТм_22.xlsx
+++ b/mode_docx_gen/pmi_gz/dtm_modes/ДТм_22.xlsx
@@ -737,86 +737,86 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="AA2" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
       </c>
       <c r="AB2" s="2" t="n">
         <v>1</v>
@@ -1242,8 +1242,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>0</v>
+      <c r="A2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
@@ -1859,9 +1859,9 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1879,9 +1879,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -2169,14 +2169,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BK2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BL2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -2234,9 +2234,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BX2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
